--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="D2">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E2">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="G2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="D3">
+        <v>42</v>
+      </c>
+      <c r="E3">
         <v>43</v>
       </c>
-      <c r="E3">
-        <v>29</v>
-      </c>
       <c r="G3">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="H3">
         <v>426</v>
